--- a/READING/5_20_12.xlsx
+++ b/READING/5_20_12.xlsx
@@ -466,16 +466,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>まま</t>
+          <t>つきあわる</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>照原样，就那样</t>
+          <t>交往</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -483,20 +483,24 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>それこそ</t>
+          <t>たびに</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>正是，恰恰是</t>
+          <t>每当...的时候</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>“および”以及</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -504,17 +508,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>当たり前</t>
+          <t>役割</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>理所当然</t>
+          <t>角色，职责</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>あたりまえ</t>
+          <t>やくわり</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -525,112 +529,124 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>積極的に</t>
+          <t>取引先</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>积极地</t>
+          <t>顾客</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>せっきょくてきに</t>
+          <t>とりひきさき</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>いまでも</t>
+          <t>〜に合わせる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>即使是现在</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>配合...，适应...</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>〜にあわせる</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>のんびりしている</t>
+          <t>受容</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>悠闲自在</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>接受，接纳</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>じゅよう</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>〜と考えると</t>
+          <t>取り組める</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>一想到…</t>
+          <t>处理;解决</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>〜とかんがえると</t>
+          <t>とりくめる</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>〜に手がつかる</t>
+          <t>切り捨てる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>着手做</t>
+          <t>置之不理</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>〜にてがつかる</t>
+          <t>きりすてる</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>さえ</t>
+          <t>一括</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>甚至，连...都</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>总括，一并</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>いっかつ</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -639,88 +655,96 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>〜といわれる</t>
+          <t>添付</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>被称为...</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>附件，附上</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>てんぷ</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>〜のは</t>
+          <t>片道</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>之所以…</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>“とは”所谓…</t>
-        </is>
-      </c>
+          <t>单程</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>かたみち</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>こころ</t>
+          <t>見直し</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>心，内心</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>重新审视，修改</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>みなおし</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>内面</t>
+          <t>落ち着かせる</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>内心，内涵</t>
+          <t>使...冷静下来</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ないめん</t>
+          <t>おちつかせる</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>〜ではない〜でもない</t>
+          <t>ぐっすり</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>既不是...也不是...</t>
+          <t>熟睡地</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -728,134 +752,134 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>仲良し</t>
+          <t>確率</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>关系好</t>
+          <t>概率</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>なかよし</t>
+          <t>かくりつ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>撮るもの</t>
+          <t>〜といわれる</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>要拍摄的东西</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>とるもの</t>
-        </is>
-      </c>
+          <t>被称为...</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>たびに</t>
+          <t>覚えている</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>每当...的时候</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>“および”以及</t>
-        </is>
-      </c>
+          <t>还记得</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>おぼえている</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>あきらめる</t>
+          <t>当たり前</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>放弃</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>理所当然</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>あたりまえ</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ぐっすり</t>
+          <t>積極的に</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>熟睡地</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>积极地</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>せっきょくてきに</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>落ち着かせる</t>
+          <t>こだわる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>使...冷静下来</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>おちつかせる</t>
-        </is>
-      </c>
+          <t>拘泥，讲究</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>〜によって</t>
+          <t>のんびりしている</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>根据...，由于...</t>
+          <t>悠闲自在</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -867,19 +891,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>見直し</t>
+          <t>やっぱり</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>重新审视，修改</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>みなおし</t>
-        </is>
-      </c>
+          <t>果然，还是</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -888,41 +908,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>片道</t>
+          <t>文書</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>单程</t>
+          <t>文件，文书</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>かたみち</t>
+          <t>ぶんしょ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ｖて＋もらう・いただく</t>
+          <t>つらい</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>我请对方为我…</t>
+          <t>辛苦的，痛苦的</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -930,20 +946,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ｖて＋くれる・くださる</t>
+          <t>〜に比例する</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>对方主动为我…</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+          <t>与...成比例</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>〜にひれいする</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -951,20 +967,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>させて＋もらう・いただく</t>
+          <t>もし</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>我请对方允许我…</t>
+          <t>如果</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>我的动作</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -972,33 +984,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>切り捨てる</t>
+          <t>ずうっと</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>置之不理</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>きりすてる</t>
-        </is>
-      </c>
+          <t>一直，始终</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>つきあわる</t>
+          <t>こんど</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>交往</t>
+          <t>这次，下次</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1006,65 +1014,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>取り組める</t>
+          <t>挨拶状</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>处理;解决</t>
+          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>とりくめる</t>
+          <t>あいさつじょう</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>受容</t>
+          <t>いつまで</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>接受，接纳</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>じゅよう</t>
-        </is>
-      </c>
+          <t>无论何时</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>〜に合わせる</t>
+          <t>だが</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>配合...，适应...</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>〜にあわせる</t>
-        </is>
-      </c>
+          <t>但是，可是</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>てすむ</t>
+          <t>あとあと</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>...就行了，...就解决了</t>
+          <t>以后，将来</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1086,21 +1086,21 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>役割</t>
+          <t>回覧</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>角色，职责</t>
+          <t>传阅</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>やくわり</t>
+          <t>かいらん</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>つながる</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>连接，联系</t>
+          <t>与...相连，导致...</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1128,61 +1128,49 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>回覧</t>
+          <t>まま</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>传阅</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>かいらん</t>
-        </is>
-      </c>
+          <t>照原样，就那样</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>文書</t>
+          <t>つながる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>文件，文书</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ぶんしょ</t>
-        </is>
-      </c>
+          <t>连接，联系</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>取引先</t>
+          <t>〜ではない〜でもない</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>顾客</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>とりひきさき</t>
-        </is>
-      </c>
+          <t>既不是...也不是...</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1191,59 +1179,55 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>挨拶状</t>
+          <t>いまでも</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>あいさつじょう</t>
-        </is>
-      </c>
+          <t>即使是现在</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>一括</t>
+          <t>〜と考えると</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>总括，一并</t>
+          <t>一想到…</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>いっかつ</t>
+          <t>〜とかんがえると</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>添付</t>
+          <t>〜に手がつかる</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>附件，附上</t>
+          <t>着手做</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>てんぷ</t>
+          <t>〜にてがつかる</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1254,19 +1238,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜に比例する</t>
+          <t>さえ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>与...成比例</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>〜にひれいする</t>
-        </is>
-      </c>
+          <t>甚至，连...都</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1275,36 +1255,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>だが</t>
+          <t>〜のは</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>但是，可是</t>
+          <t>之所以…</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>“とは”所谓…</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>確率</t>
+          <t>こころ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>概率</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>かくりつ</t>
-        </is>
-      </c>
+          <t>心，内心</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1313,15 +1293,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>内面</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>内心，内涵</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ないめん</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1330,29 +1314,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>もし</t>
+          <t>仲良し</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>如果</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>关系好</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>なかよし</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>つらい</t>
+          <t>てすむ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>辛苦的，痛苦的</t>
+          <t>...就行了，...就解决了</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1364,15 +1352,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>あとあと</t>
+          <t>撮るもの</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>以后，将来</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>要拍摄的东西</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>とるもの</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1381,12 +1373,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ずうっと</t>
+          <t>あきらめる</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>一直，始终</t>
+          <t>放弃</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1394,41 +1386,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>覚えている</t>
+          <t>〜によって</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>还记得</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>おぼえている</t>
-        </is>
-      </c>
+          <t>根据...，由于...</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>やっぱり</t>
+          <t>Ｖて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>果然，还是</t>
+          <t>我请对方为我…</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1436,16 +1428,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>こんど</t>
+          <t>Ｖて＋くれる・くださる</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>这次，下次</t>
+          <t>对方主动为我…</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1453,29 +1449,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>いつまで</t>
+          <t>させて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>无论何时</t>
+          <t>我请对方允许我…</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>我的动作</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>こだわる</t>
+          <t>それこそ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>拘泥，讲究</t>
+          <t>正是，恰恰是</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>

--- a/READING/5_20_12.xlsx
+++ b/READING/5_20_12.xlsx
@@ -466,269 +466,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>つきあわる</t>
+          <t>見直し</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>交往</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>重新审视，修改</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>みなおし</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>たびに</t>
+          <t>切り捨てる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>每当...的时候</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>“および”以及</t>
-        </is>
-      </c>
+          <t>置之不理</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>きりすてる</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>役割</t>
+          <t>こだわる</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>角色，职责</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>やくわり</t>
-        </is>
-      </c>
+          <t>拘泥，讲究</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>取引先</t>
+          <t>つきあわる</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>顾客</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>とりひきさき</t>
-        </is>
-      </c>
+          <t>交往</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜に合わせる</t>
+          <t>受容</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>配合...，适应...</t>
+          <t>接受，接纳</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>〜にあわせる</t>
+          <t>じゅよう</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>受容</t>
+          <t>役割</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>接受，接纳</t>
+          <t>角色，职责</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>じゅよう</t>
+          <t>やくわり</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>取り組める</t>
+          <t>覚えている</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>处理;解决</t>
+          <t>还记得</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>とりくめる</t>
+          <t>おぼえている</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>切り捨てる</t>
+          <t>当たり前</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>置之不理</t>
+          <t>理所当然</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>きりすてる</t>
+          <t>あたりまえ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>一括</t>
+          <t>つらい</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>总括，一并</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>いっかつ</t>
-        </is>
-      </c>
+          <t>辛苦的，痛苦的</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>添付</t>
+          <t>片道</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>附件，附上</t>
+          <t>单程</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>てんぷ</t>
+          <t>かたみち</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>片道</t>
+          <t>〜といわれる</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>单程</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>かたみち</t>
-        </is>
-      </c>
+          <t>被称为...</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>見直し</t>
+          <t>のんびりしている</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>重新审视，修改</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>みなおし</t>
-        </is>
-      </c>
+          <t>悠闲自在</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>落ち着かせる</t>
+          <t>取り組める</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>使...冷静下来</t>
+          <t>处理;解决</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>おちつかせる</t>
+          <t>とりくめる</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -739,53 +723,57 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ぐっすり</t>
+          <t>文書</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>熟睡地</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>文件，文书</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ぶんしょ</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>確率</t>
+          <t>ぐっすり</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>概率</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>かくりつ</t>
-        </is>
-      </c>
+          <t>熟睡地</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜といわれる</t>
+          <t>積極的に</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>被称为...</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>积极地</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>せっきょくてきに</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -794,95 +782,95 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>覚えている</t>
+          <t>落ち着かせる</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>还记得</t>
+          <t>使...冷静下来</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>おぼえている</t>
+          <t>おちつかせる</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>当たり前</t>
+          <t>ずうっと</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>理所当然</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>あたりまえ</t>
-        </is>
-      </c>
+          <t>一直，始终</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>積極的に</t>
+          <t>やっぱり</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>积极地</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>せっきょくてきに</t>
-        </is>
-      </c>
+          <t>果然，还是</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>こだわる</t>
+          <t>たびに</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>拘泥，讲究</t>
+          <t>每当...的时候</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>“および”以及</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>のんびりしている</t>
+          <t>一括</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>悠闲自在</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>总括，一并</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>いっかつ</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -891,15 +879,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>やっぱり</t>
+          <t>添付</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>果然，还是</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>附件，附上</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>てんぷ</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -908,33 +900,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>文書</t>
+          <t>確率</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>文件，文书</t>
+          <t>概率</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ぶんしょ</t>
+          <t>かくりつ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>つらい</t>
+          <t>こころ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>辛苦的，痛苦的</t>
+          <t>心，内心</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -942,40 +934,40 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>〜に比例する</t>
+          <t>あきらめる</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>与...成比例</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>〜にひれいする</t>
-        </is>
-      </c>
+          <t>放弃</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>もし</t>
+          <t>取引先</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>如果</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>顾客</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>とりひきさき</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -984,15 +976,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ずうっと</t>
+          <t>〜に合わせる</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>一直，始终</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>配合...，适应...</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>〜にあわせる</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1001,15 +997,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>こんど</t>
+          <t>仲良し</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>这次，下次</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>关系好</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>なかよし</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>挨拶状</t>
+          <t>撮るもの</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
+          <t>要拍摄的东西</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>あいさつじょう</t>
+          <t>とるもの</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1039,16 +1039,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>いつまで</t>
+          <t>〜のは</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>无论何时</t>
+          <t>之所以…</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>“とは”所谓…</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1056,15 +1060,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>だが</t>
+          <t>内面</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>但是，可是</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>内心，内涵</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ないめん</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1073,12 +1081,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>あとあと</t>
+          <t>さえ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>以后，将来</t>
+          <t>甚至，连...都</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1090,19 +1098,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>回覧</t>
+          <t>てすむ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>传阅</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>かいらん</t>
-        </is>
-      </c>
+          <t>...就行了，...就解决了</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1111,16 +1115,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>Ｖて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
+          <t>我请对方为我…</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1128,12 +1136,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>まま</t>
+          <t>〜によって</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>照原样，就那样</t>
+          <t>根据...，由于...</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1145,16 +1153,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>つながる</t>
+          <t>させて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>连接，联系</t>
+          <t>我请对方允许我…</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>我的动作</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1162,16 +1174,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>〜ではない〜でもない</t>
+          <t>Ｖて＋くれる・くださる</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>既不是...也不是...</t>
+          <t>对方主动为我…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1179,12 +1195,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>いまでも</t>
+          <t>それこそ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>即使是现在</t>
+          <t>正是，恰恰是</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1196,17 +1212,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>〜と考えると</t>
+          <t>〜に手がつかる</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>一想到…</t>
+          <t>着手做</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>〜とかんがえると</t>
+          <t>〜にてがつかる</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1217,19 +1233,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>〜に手がつかる</t>
+          <t>こんど</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>着手做</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>〜にてがつかる</t>
-        </is>
-      </c>
+          <t>这次，下次</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1238,15 +1250,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>さえ</t>
+          <t>〜と考えると</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>甚至，连...都</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>一想到…</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>〜とかんがえると</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1255,20 +1271,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>〜のは</t>
+          <t>いまでも</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>之所以…</t>
+          <t>即使是现在</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>“とは”所谓…</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1276,12 +1288,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>こころ</t>
+          <t>つながる</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>心，内心</t>
+          <t>连接，联系</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1293,19 +1305,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>内面</t>
+          <t>まま</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>内心，内涵</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ないめん</t>
-        </is>
-      </c>
+          <t>照原样，就那样</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1314,19 +1322,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>仲良し</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>关系好</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>なかよし</t>
-        </is>
-      </c>
+          <t>与...相连，导致...</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1335,12 +1339,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>てすむ</t>
+          <t>〜ではない〜でもない</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>...就行了，...就解决了</t>
+          <t>既不是...也不是...</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1352,19 +1356,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>撮るもの</t>
+          <t>あとあと</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>要拍摄的东西</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>とるもの</t>
-        </is>
-      </c>
+          <t>以后，将来</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1373,15 +1373,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>あきらめる</t>
+          <t>回覧</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>放弃</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>传阅</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>かいらん</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1390,12 +1394,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>〜によって</t>
+          <t>だが</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>根据...，由于...</t>
+          <t>但是，可是</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1407,20 +1411,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ｖて＋もらう・いただく</t>
+          <t>いつまで</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>我请对方为我…</t>
+          <t>无论何时</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1428,20 +1428,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ｖて＋くれる・くださる</t>
+          <t>挨拶状</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>对方主动为我…</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>あいさつじょう</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1449,20 +1449,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>させて＋もらう・いただく</t>
+          <t>もし</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>我请对方允许我…</t>
+          <t>如果</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>我的动作</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1470,15 +1466,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>それこそ</t>
+          <t>〜に比例する</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>正是，恰恰是</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>与...成比例</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>〜にひれいする</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">

--- a/READING/5_20_12.xlsx
+++ b/READING/5_20_12.xlsx
@@ -491,74 +491,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>切り捨てる</t>
+          <t>こだわる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>置之不理</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>きりすてる</t>
-        </is>
-      </c>
+          <t>拘泥，讲究</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>こだわる</t>
+          <t>受容</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>拘泥，讲究</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>接受，接纳</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>じゅよう</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>つきあわる</t>
+          <t>切り捨てる</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>交往</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>置之不理</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>きりすてる</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>受容</t>
+          <t>つきあわる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>接受，接纳</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>じゅよう</t>
-        </is>
-      </c>
+          <t>交往</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -630,12 +630,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>つらい</t>
+          <t>〜といわれる</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>辛苦的，痛苦的</t>
+          <t>被称为...</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -647,17 +647,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>片道</t>
+          <t>取り組める</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>单程</t>
+          <t>处理;解决</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>かたみち</t>
+          <t>とりくめる</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -668,12 +668,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>〜といわれる</t>
+          <t>のんびりしている</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>被称为...</t>
+          <t>悠闲自在</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -685,15 +685,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>のんびりしている</t>
+          <t>片道</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>悠闲自在</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>单程</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>かたみち</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -702,19 +706,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>取り組める</t>
+          <t>つらい</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>处理;解决</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>とりくめる</t>
-        </is>
-      </c>
+          <t>辛苦的，痛苦的</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -803,15 +803,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ずうっと</t>
+          <t>確率</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>一直，始终</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>概率</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>かくりつ</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -820,15 +824,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>やっぱり</t>
+          <t>〜に合わせる</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>果然，还是</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>配合...，适应...</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>〜にあわせる</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -837,20 +845,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>たびに</t>
+          <t>取引先</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>每当...的时候</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>“および”以及</t>
-        </is>
-      </c>
+          <t>顾客</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>とりひきさき</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -858,19 +866,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>一括</t>
+          <t>あきらめる</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>总括，一并</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>いっかつ</t>
-        </is>
-      </c>
+          <t>放弃</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -879,19 +883,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>添付</t>
+          <t>こころ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>附件，附上</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>てんぷ</t>
-        </is>
-      </c>
+          <t>心，内心</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -900,17 +900,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>確率</t>
+          <t>一括</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>概率</t>
+          <t>总括，一并</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>かくりつ</t>
+          <t>いっかつ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -921,15 +921,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>こころ</t>
+          <t>添付</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>心，内心</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>附件，附上</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>てんぷ</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -938,16 +942,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>あきらめる</t>
+          <t>たびに</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>放弃</t>
+          <t>每当...的时候</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>“および”以及</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -955,19 +963,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>取引先</t>
+          <t>やっぱり</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>顾客</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>とりひきさき</t>
-        </is>
-      </c>
+          <t>果然，还是</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -976,19 +980,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>〜に合わせる</t>
+          <t>ずうっと</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>配合...，适应...</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>〜にあわせる</t>
-        </is>
-      </c>
+          <t>一直，始终</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -997,17 +997,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>仲良し</t>
+          <t>回覧</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>关系好</t>
+          <t>传阅</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>なかよし</t>
+          <t>かいらん</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1018,19 +1018,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>撮るもの</t>
+          <t>つながる</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>要拍摄的东西</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>とるもの</t>
-        </is>
-      </c>
+          <t>连接，联系</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1039,20 +1035,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>〜のは</t>
+          <t>まま</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>之所以…</t>
+          <t>照原样，就那样</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>“とは”所谓…</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1060,19 +1052,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>内面</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>内心，内涵</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ないめん</t>
-        </is>
-      </c>
+          <t>与...相连，导致...</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1081,12 +1069,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>さえ</t>
+          <t>〜ではない〜でもない</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>甚至，连...都</t>
+          <t>既不是...也不是...</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1098,12 +1086,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>てすむ</t>
+          <t>あとあと</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>...就行了，...就解决了</t>
+          <t>以后，将来</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1115,20 +1103,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ｖて＋もらう・いただく</t>
+          <t>いつまで</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>我请对方为我…</t>
+          <t>无论何时</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1136,12 +1120,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>〜によって</t>
+          <t>だが</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>根据...，由于...</t>
+          <t>但是，可是</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1153,20 +1137,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>させて＋もらう・いただく</t>
+          <t>〜と考えると</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>我请对方允许我…</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>我的动作</t>
-        </is>
-      </c>
+          <t>一想到…</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>〜とかんがえると</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1174,20 +1158,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ｖて＋くれる・くださる</t>
+          <t>挨拶状</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>对方主动为我…</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>あいさつじょう</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1195,12 +1179,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>それこそ</t>
+          <t>もし</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>正是，恰恰是</t>
+          <t>如果</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1212,17 +1196,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>〜に手がつかる</t>
+          <t>〜に比例する</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>着手做</t>
+          <t>与...成比例</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>〜にてがつかる</t>
+          <t>〜にひれいする</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1233,12 +1217,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>こんど</t>
+          <t>いまでも</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>这次，下次</t>
+          <t>即使是现在</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1250,17 +1234,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜と考えると</t>
+          <t>仲良し</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>一想到…</t>
+          <t>关系好</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>〜とかんがえると</t>
+          <t>なかよし</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1271,12 +1255,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>いまでも</t>
+          <t>こんど</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>即使是现在</t>
+          <t>这次，下次</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1288,15 +1272,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>つながる</t>
+          <t>〜に手がつかる</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>连接，联系</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>着手做</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>〜にてがつかる</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1305,12 +1293,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>まま</t>
+          <t>それこそ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>照原样，就那样</t>
+          <t>正是，恰恰是</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1322,16 +1310,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>Ｖて＋くれる・くださる</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
+          <t>对方主动为我…</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1339,16 +1331,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>〜ではない〜でもない</t>
+          <t>させて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>既不是...也不是...</t>
+          <t>我请对方允许我…</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>我的动作</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1356,12 +1352,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>あとあと</t>
+          <t>〜によって</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>以后，将来</t>
+          <t>根据...，由于...</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1373,20 +1369,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>回覧</t>
+          <t>Ｖて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>传阅</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>かいらん</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>我请对方为我…</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1394,12 +1390,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>だが</t>
+          <t>てすむ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>但是，可是</t>
+          <t>...就行了，...就解决了</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1411,12 +1407,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>いつまで</t>
+          <t>さえ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>无论何时</t>
+          <t>甚至，连...都</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1428,17 +1424,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>挨拶状</t>
+          <t>内面</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
+          <t>内心，内涵</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>あいさつじょう</t>
+          <t>ないめん</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1449,16 +1445,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>もし</t>
+          <t>〜のは</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>如果</t>
+          <t>之所以…</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>“とは”所谓…</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>〜に比例する</t>
+          <t>撮るもの</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>与...成比例</t>
+          <t>要拍摄的东西</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>〜にひれいする</t>
+          <t>とるもの</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>

--- a/READING/5_20_12.xlsx
+++ b/READING/5_20_12.xlsx
@@ -466,33 +466,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>まま</t>
+          <t>見直し</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>照原样，就那样</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>重新审视，修改</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>みなおし</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>それこそ</t>
+          <t>こだわる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>正是，恰恰是</t>
+          <t>拘泥，讲究</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -500,58 +504,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>当たり前</t>
+          <t>受容</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>理所当然</t>
+          <t>接受，接纳</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>あたりまえ</t>
+          <t>じゅよう</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>積極的に</t>
+          <t>切り捨てる</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>积极地</t>
+          <t>置之不理</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>せっきょくてきに</t>
+          <t>きりすてる</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>いまでも</t>
+          <t>つきあわる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>即使是现在</t>
+          <t>交往</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -559,75 +563,79 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>のんびりしている</t>
+          <t>役割</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>悠闲自在</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>角色，职责</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>やくわり</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>〜と考えると</t>
+          <t>覚えている</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>一想到…</t>
+          <t>还记得</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>〜とかんがえると</t>
+          <t>おぼえている</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>〜に手がつかる</t>
+          <t>当たり前</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>着手做</t>
+          <t>理所当然</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>〜にてがつかる</t>
+          <t>あたりまえ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>さえ</t>
+          <t>〜といわれる</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>甚至，连...都</t>
+          <t>被称为...</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -635,175 +643,179 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>〜といわれる</t>
+          <t>取り組める</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>被称为...</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>处理;解决</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>とりくめる</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>〜のは</t>
+          <t>のんびりしている</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>之所以…</t>
+          <t>悠闲自在</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>“とは”所谓…</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>こころ</t>
+          <t>片道</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>心，内心</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>单程</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>かたみち</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>内面</t>
+          <t>つらい</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>内心，内涵</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ないめん</t>
-        </is>
-      </c>
+          <t>辛苦的，痛苦的</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>〜ではない〜でもない</t>
+          <t>文書</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>既不是...也不是...</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>文件，文书</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ぶんしょ</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>仲良し</t>
+          <t>ぐっすり</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>关系好</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>なかよし</t>
-        </is>
-      </c>
+          <t>熟睡地</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>撮るもの</t>
+          <t>積極的に</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>要拍摄的东西</t>
+          <t>积极地</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>とるもの</t>
+          <t>せっきょくてきに</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>たびに</t>
+          <t>落ち着かせる</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>每当...的时候</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>“および”以及</t>
-        </is>
-      </c>
+          <t>使...冷静下来</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>おちつかせる</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>あきらめる</t>
+          <t>確率</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>放弃</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>概率</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>かくりつ</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -812,15 +824,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ぐっすり</t>
+          <t>〜に合わせる</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>熟睡地</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>配合...，适应...</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>〜にあわせる</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -829,33 +845,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>落ち着かせる</t>
+          <t>取引先</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>使...冷静下来</t>
+          <t>顾客</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>おちつかせる</t>
+          <t>とりひきさき</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>〜によって</t>
+          <t>あきらめる</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>根据...，由于...</t>
+          <t>放弃</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -867,19 +883,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>見直し</t>
+          <t>こころ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>重新审视，修改</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>みなおし</t>
-        </is>
-      </c>
+          <t>心，内心</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -888,83 +900,79 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>片道</t>
+          <t>一括</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>单程</t>
+          <t>总括，一并</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>かたみち</t>
+          <t>いっかつ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ｖて＋もらう・いただく</t>
+          <t>添付</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>我请对方为我…</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+          <t>附件，附上</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>てんぷ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ｖて＋くれる・くださる</t>
+          <t>たびに</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>对方主动为我…</t>
+          <t>每当...的时候</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>对方动作</t>
+          <t>“および”以及</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>させて＋もらう・いただく</t>
+          <t>やっぱり</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>我请对方允许我…</t>
+          <t>果然，还是</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>我的动作</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -972,99 +980,87 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>切り捨てる</t>
+          <t>ずうっと</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>置之不理</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>きりすてる</t>
-        </is>
-      </c>
+          <t>一直，始终</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>つきあわる</t>
+          <t>回覧</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>交往</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>传阅</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>かいらん</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>取り組める</t>
+          <t>つながる</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>处理;解决</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>とりくめる</t>
-        </is>
-      </c>
+          <t>连接，联系</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>受容</t>
+          <t>まま</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>接受，接纳</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>じゅよう</t>
-        </is>
-      </c>
+          <t>照原样，就那样</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>〜に合わせる</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>配合...，适应...</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>〜にあわせる</t>
-        </is>
-      </c>
+          <t>与...相连，导致...</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1073,12 +1069,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>てすむ</t>
+          <t>〜ではない〜でもない</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>...就行了，...就解决了</t>
+          <t>既不是...也不是...</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1086,23 +1082,19 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>役割</t>
+          <t>あとあと</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>角色，职责</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>やくわり</t>
-        </is>
-      </c>
+          <t>以后，将来</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1111,12 +1103,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>つながる</t>
+          <t>いつまで</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>连接，联系</t>
+          <t>无论何时</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1128,59 +1120,55 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>回覧</t>
+          <t>だが</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>传阅</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>かいらん</t>
-        </is>
-      </c>
+          <t>但是，可是</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>文書</t>
+          <t>〜と考えると</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>文件，文书</t>
+          <t>一想到…</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ぶんしょ</t>
+          <t>〜とかんがえると</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>取引先</t>
+          <t>挨拶状</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>顾客</t>
+          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>とりひきさき</t>
+          <t>あいさつじょう</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1191,61 +1179,53 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>挨拶状</t>
+          <t>もし</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>あいさつじょう</t>
-        </is>
-      </c>
+          <t>如果</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>一括</t>
+          <t>〜に比例する</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>总括，一并</t>
+          <t>与...成比例</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>いっかつ</t>
+          <t>〜にひれいする</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>添付</t>
+          <t>いまでも</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>附件，附上</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>てんぷ</t>
-        </is>
-      </c>
+          <t>即使是现在</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1254,17 +1234,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜に比例する</t>
+          <t>仲良し</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>与...成比例</t>
+          <t>关系好</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>〜にひれいする</t>
+          <t>なかよし</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1275,12 +1255,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>だが</t>
+          <t>こんど</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>但是，可是</t>
+          <t>这次，下次</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1288,21 +1268,21 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>確率</t>
+          <t>〜に手がつかる</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>概率</t>
+          <t>着手做</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>かくりつ</t>
+          <t>〜にてがつかる</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1313,12 +1293,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>それこそ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
+          <t>正是，恰恰是</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1330,33 +1310,41 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>もし</t>
+          <t>Ｖて＋くれる・くださる</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>如果</t>
+          <t>对方主动为我…</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>つらい</t>
+          <t>させて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>辛苦的，痛苦的</t>
+          <t>我请对方允许我…</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>我的动作</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1364,12 +1352,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>あとあと</t>
+          <t>〜によって</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>以后，将来</t>
+          <t>根据...，由于...</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1381,50 +1369,50 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ずうっと</t>
+          <t>Ｖて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>一直，始终</t>
+          <t>我请对方为我…</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>覚えている</t>
+          <t>てすむ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>还记得</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>おぼえている</t>
-        </is>
-      </c>
+          <t>...就行了，...就解决了</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>やっぱり</t>
+          <t>さえ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>果然，还是</t>
+          <t>甚至，连...都</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1436,15 +1424,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>こんど</t>
+          <t>内面</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>这次，下次</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>内心，内涵</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ないめん</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1453,32 +1445,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>いつまで</t>
+          <t>〜のは</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>无论何时</t>
+          <t>之所以…</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>“とは”所谓…</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>こだわる</t>
+          <t>撮るもの</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>拘泥，讲究</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>要拍摄的东西</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>とるもの</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">

--- a/READING/5_20_12.xlsx
+++ b/READING/5_20_12.xlsx
@@ -466,37 +466,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>見直し</t>
+          <t>まま</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>重新审视，修改</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>みなおし</t>
-        </is>
-      </c>
+          <t>照原样，就那样</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>こだわる</t>
+          <t>それこそ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>拘泥，讲究</t>
+          <t>正是，恰恰是</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -504,58 +500,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>受容</t>
+          <t>当たり前</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>接受，接纳</t>
+          <t>理所当然</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>じゅよう</t>
+          <t>あたりまえ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>切り捨てる</t>
+          <t>積極的に</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>置之不理</t>
+          <t>积极地</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>きりすてる</t>
+          <t>せっきょくてきに</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>つきあわる</t>
+          <t>いまでも</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>交往</t>
+          <t>即使是现在</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -563,79 +559,75 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>役割</t>
+          <t>のんびりしている</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>角色，职责</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>やくわり</t>
-        </is>
-      </c>
+          <t>悠闲自在</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>覚えている</t>
+          <t>〜と考えると</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>还记得</t>
+          <t>一想到…</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>おぼえている</t>
+          <t>〜とかんがえると</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>当たり前</t>
+          <t>〜に手がつかる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>理所当然</t>
+          <t>着手做</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>あたりまえ</t>
+          <t>〜にてがつかる</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>〜といわれる</t>
+          <t>さえ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>被称为...</t>
+          <t>甚至，连...都</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -643,179 +635,175 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>取り組める</t>
+          <t>〜といわれる</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>处理;解决</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>とりくめる</t>
-        </is>
-      </c>
+          <t>被称为...</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>のんびりしている</t>
+          <t>〜のは</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>悠闲自在</t>
+          <t>之所以…</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>“とは”所谓…</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>片道</t>
+          <t>こころ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>单程</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>かたみち</t>
-        </is>
-      </c>
+          <t>心，内心</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>つらい</t>
+          <t>内面</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>辛苦的，痛苦的</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>内心，内涵</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ないめん</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>文書</t>
+          <t>〜ではない〜でもない</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>文件，文书</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ぶんしょ</t>
-        </is>
-      </c>
+          <t>既不是...也不是...</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ぐっすり</t>
+          <t>仲良し</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>熟睡地</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>关系好</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>なかよし</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>積極的に</t>
+          <t>撮るもの</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>积极地</t>
+          <t>要拍摄的东西</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>せっきょくてきに</t>
+          <t>とるもの</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>落ち着かせる</t>
+          <t>たびに</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>使...冷静下来</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>おちつかせる</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>每当...的时候</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>“および”以及</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>確率</t>
+          <t>あきらめる</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>概率</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>かくりつ</t>
-        </is>
-      </c>
+          <t>放弃</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -824,19 +812,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>〜に合わせる</t>
+          <t>ぐっすり</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>配合...，适应...</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>〜にあわせる</t>
-        </is>
-      </c>
+          <t>熟睡地</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -845,33 +829,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>取引先</t>
+          <t>落ち着かせる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>顾客</t>
+          <t>使...冷静下来</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>とりひきさき</t>
+          <t>おちつかせる</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>あきらめる</t>
+          <t>〜によって</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>放弃</t>
+          <t>根据...，由于...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -883,15 +867,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>こころ</t>
+          <t>見直し</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>心，内心</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>重新审视，修改</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>みなおし</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -900,79 +888,83 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>一括</t>
+          <t>片道</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>总括，一并</t>
+          <t>单程</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>いっかつ</t>
+          <t>かたみち</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>添付</t>
+          <t>Ｖて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>附件，附上</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>てんぷ</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>我请对方为我…</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>对方动作</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>たびに</t>
+          <t>Ｖて＋くれる・くださる</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>每当...的时候</t>
+          <t>对方主动为我…</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>“および”以及</t>
+          <t>对方动作</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>やっぱり</t>
+          <t>させて＋もらう・いただく</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>果然，还是</t>
+          <t>我请对方允许我…</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>我的动作</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -980,87 +972,99 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ずうっと</t>
+          <t>切り捨てる</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>一直，始终</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>置之不理</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>きりすてる</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>回覧</t>
+          <t>つきあわる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>传阅</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>かいらん</t>
-        </is>
-      </c>
+          <t>交往</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>つながる</t>
+          <t>取り組める</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>连接，联系</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>处理;解决</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>とりくめる</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>まま</t>
+          <t>受容</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>照原样，就那样</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>接受，接纳</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>じゅよう</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>〜に合わせる</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>配合...，适应...</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>〜にあわせる</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1069,12 +1073,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>〜ではない〜でもない</t>
+          <t>てすむ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>既不是...也不是...</t>
+          <t>...就行了，...就解决了</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1082,19 +1086,23 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>あとあと</t>
+          <t>役割</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>以后，将来</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>角色，职责</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>やくわり</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1103,12 +1111,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>いつまで</t>
+          <t>つながる</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>无论何时</t>
+          <t>连接，联系</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1120,55 +1128,59 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>だが</t>
+          <t>回覧</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>但是，可是</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>传阅</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>かいらん</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>〜と考えると</t>
+          <t>文書</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>一想到…</t>
+          <t>文件，文书</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>〜とかんがえると</t>
+          <t>ぶんしょ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>挨拶状</t>
+          <t>取引先</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
+          <t>顾客</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>あいさつじょう</t>
+          <t>とりひきさき</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1179,53 +1191,61 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>もし</t>
+          <t>挨拶状</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>如果</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>问候信，（公司搬迁、人事变动等的）通知函</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>あいさつじょう</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>〜に比例する</t>
+          <t>一括</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>与...成比例</t>
+          <t>总括，一并</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>〜にひれいする</t>
+          <t>いっかつ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>いまでも</t>
+          <t>添付</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>即使是现在</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>附件，附上</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>てんぷ</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1234,17 +1254,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>仲良し</t>
+          <t>〜に比例する</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>关系好</t>
+          <t>与...成比例</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>なかよし</t>
+          <t>〜にひれいする</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1255,12 +1275,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>こんど</t>
+          <t>だが</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>这次，下次</t>
+          <t>但是，可是</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1268,21 +1288,21 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>〜に手がつかる</t>
+          <t>確率</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>着手做</t>
+          <t>概率</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>〜にてがつかる</t>
+          <t>かくりつ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1293,12 +1313,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>それこそ</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>正是，恰恰是</t>
+          <t>与...相连，导致...</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1310,41 +1330,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ｖて＋くれる・くださる</t>
+          <t>もし</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>对方主动为我…</t>
+          <t>如果</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>させて＋もらう・いただく</t>
+          <t>つらい</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>我请对方允许我…</t>
+          <t>辛苦的，痛苦的</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>我的动作</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1352,12 +1364,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>〜によって</t>
+          <t>あとあと</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>根据...，由于...</t>
+          <t>以后，将来</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1369,50 +1381,50 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ｖて＋もらう・いただく</t>
+          <t>ずうっと</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>我请对方为我…</t>
+          <t>一直，始终</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>对方动作</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>てすむ</t>
+          <t>覚えている</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>...就行了，...就解决了</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>还记得</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>おぼえている</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>さえ</t>
+          <t>やっぱり</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>甚至，连...都</t>
+          <t>果然，还是</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1424,19 +1436,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>内面</t>
+          <t>こんど</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>内心，内涵</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ないめん</t>
-        </is>
-      </c>
+          <t>这次，下次</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1445,40 +1453,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>〜のは</t>
+          <t>いつまで</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>之所以…</t>
+          <t>无论何时</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>“とは”所谓…</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>撮るもの</t>
+          <t>こだわる</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>要拍摄的东西</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>とるもの</t>
-        </is>
-      </c>
+          <t>拘泥，讲究</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
